--- a/Assets/Resources/MasterData/EventData.xlsx
+++ b/Assets/Resources/MasterData/EventData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Unitydata\Droad\Assets\Resources\MasterData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ban10\Documents\Program\Droad\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E482292C-DBA0-4220-BE48-FD97200FA494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B538E3B-06FF-4E49-A5A9-238D1D6442B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EventData" sheetId="1" r:id="rId1"/>
@@ -581,11 +581,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1043,10 +1042,10 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="1">
         <v>-1</v>
       </c>
       <c r="C8" s="1">
@@ -1059,18 +1058,18 @@
       <c r="E8" s="1">
         <v>-1</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="1">
         <v>-1</v>
       </c>
       <c r="C9" s="1">
@@ -1083,18 +1082,18 @@
       <c r="E9" s="1">
         <v>-1</v>
       </c>
-      <c r="F9" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="F9" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="1">
         <v>-1</v>
       </c>
       <c r="C10" s="1">
@@ -1107,18 +1106,18 @@
       <c r="E10" s="1">
         <v>-1</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="1">
         <v>9</v>
       </c>
       <c r="C11" s="1">
@@ -1131,18 +1130,18 @@
       <c r="E11" s="1">
         <v>-1</v>
       </c>
-      <c r="F11" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="F11" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="1">
         <v>110</v>
       </c>
       <c r="C12" s="1">
@@ -1155,18 +1154,18 @@
       <c r="E12" s="1">
         <v>-1</v>
       </c>
-      <c r="F12" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G12" s="3">
+      <c r="F12" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="1">
         <v>111</v>
       </c>
       <c r="C13" s="1">
@@ -1179,7 +1178,7 @@
       <c r="E13" s="1">
         <v>-1</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="1">
         <v>-1</v>
       </c>
       <c r="G13" s="1">
@@ -1187,10 +1186,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="1">
         <v>112</v>
       </c>
       <c r="C14" s="1">
@@ -1203,7 +1202,7 @@
       <c r="E14" s="1">
         <v>-1</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="1">
         <v>-1</v>
       </c>
       <c r="G14" s="1">
@@ -1211,10 +1210,10 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="1">
         <v>113</v>
       </c>
       <c r="C15" s="1">
@@ -1227,18 +1226,18 @@
       <c r="E15" s="1">
         <v>-1</v>
       </c>
-      <c r="F15" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="F15" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G15" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="1">
         <v>6</v>
       </c>
       <c r="C16" s="1">
@@ -1251,18 +1250,18 @@
       <c r="E16" s="1">
         <v>-1</v>
       </c>
-      <c r="F16" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G16" s="3">
+      <c r="F16" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G16" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="1">
         <v>11</v>
       </c>
       <c r="C17" s="1">
@@ -1275,18 +1274,18 @@
       <c r="E17" s="1">
         <v>-1</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="1">
         <v>10</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="1">
         <v>12</v>
       </c>
       <c r="C18" s="1">
@@ -1299,18 +1298,18 @@
       <c r="E18" s="1">
         <v>-1</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="1">
         <v>2</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="1">
         <v>13</v>
       </c>
       <c r="C19" s="1">
@@ -1323,18 +1322,18 @@
       <c r="E19" s="1">
         <v>-1</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="1">
         <v>1</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="1">
         <v>10</v>
       </c>
       <c r="C20" s="1">
@@ -1347,18 +1346,18 @@
       <c r="E20" s="1">
         <v>-1</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="1">
         <v>1</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="1">
         <v>14</v>
       </c>
       <c r="C21" s="1">
@@ -1371,18 +1370,18 @@
       <c r="E21" s="1">
         <v>5</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G21" s="3">
+      <c r="F21" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="1">
         <v>15</v>
       </c>
       <c r="C22" s="1">
@@ -1395,18 +1394,18 @@
       <c r="E22" s="1">
         <v>6</v>
       </c>
-      <c r="F22" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="F22" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G22" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="1">
         <v>16</v>
       </c>
       <c r="C23" s="1">
@@ -1419,18 +1418,18 @@
       <c r="E23" s="1">
         <v>-1</v>
       </c>
-      <c r="F23" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G23" s="3">
+      <c r="F23" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G23" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="1">
         <v>8</v>
       </c>
       <c r="C24" s="1">
@@ -1443,18 +1442,18 @@
       <c r="E24" s="1">
         <v>-1</v>
       </c>
-      <c r="F24" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="F24" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G24" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="1">
         <v>9</v>
       </c>
       <c r="C25" s="1">
@@ -1467,18 +1466,18 @@
       <c r="E25" s="1">
         <v>-1</v>
       </c>
-      <c r="F25" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G25" s="3">
+      <c r="F25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G25" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="1">
         <v>17</v>
       </c>
       <c r="C26" s="1">
@@ -1491,18 +1490,18 @@
       <c r="E26" s="1">
         <v>-1</v>
       </c>
-      <c r="F26" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G26" s="3">
+      <c r="F26" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G26" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="1">
         <v>18</v>
       </c>
       <c r="C27" s="1">
@@ -1515,18 +1514,18 @@
       <c r="E27" s="1">
         <v>-1</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="1">
         <v>10</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="1">
         <v>19</v>
       </c>
       <c r="C28" s="1">
@@ -1539,18 +1538,18 @@
       <c r="E28" s="1">
         <v>-1</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="1">
         <v>3</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="1">
         <v>20</v>
       </c>
       <c r="C29" s="1">
@@ -1563,18 +1562,18 @@
       <c r="E29" s="1">
         <v>-1</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="1">
         <v>0</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="1">
         <v>12</v>
       </c>
       <c r="C30" s="1">
@@ -1587,18 +1586,18 @@
       <c r="E30" s="1">
         <v>-1</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="1">
         <v>3</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="1">
         <v>-1</v>
       </c>
       <c r="C31" s="1">
@@ -1611,18 +1610,18 @@
       <c r="E31" s="1">
         <v>-1</v>
       </c>
-      <c r="F31" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G31" s="3">
+      <c r="F31" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G31" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="1">
         <v>-1</v>
       </c>
       <c r="C32" s="1">
@@ -1635,18 +1634,18 @@
       <c r="E32" s="1">
         <v>-1</v>
       </c>
-      <c r="F32" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="F32" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G32" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="1">
         <v>-1</v>
       </c>
       <c r="C33" s="1">
@@ -1659,18 +1658,18 @@
       <c r="E33" s="1">
         <v>-1</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="1">
         <v>3</v>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="1">
         <v>-1</v>
       </c>
       <c r="C34" s="1">
@@ -1683,18 +1682,18 @@
       <c r="E34" s="1">
         <v>-1</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="1">
         <v>3</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="1">
         <v>-1</v>
       </c>
       <c r="C35" s="1">
@@ -1707,18 +1706,18 @@
       <c r="E35" s="1">
         <v>-1</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1</v>
-      </c>
-      <c r="G35" s="3">
+      <c r="F35" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G35" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="1">
         <v>-1</v>
       </c>
       <c r="C36" s="1">
@@ -1731,18 +1730,18 @@
       <c r="E36" s="1">
         <v>-1</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="1">
         <v>10</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="3">
+      <c r="B37" s="1">
         <v>-1</v>
       </c>
       <c r="C37" s="1">
@@ -1755,18 +1754,18 @@
       <c r="E37" s="1">
         <v>-1</v>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="1">
         <v>10</v>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="3">
+      <c r="B38" s="1">
         <v>-1</v>
       </c>
       <c r="C38" s="1">
@@ -1776,21 +1775,21 @@
       <c r="D38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E38" s="1">
         <v>15</v>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="1">
         <v>1</v>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="1">
         <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="3">
-        <v>36</v>
-      </c>
-      <c r="B39" s="3">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1">
         <v>-1</v>
       </c>
       <c r="C39" s="1">
@@ -1800,13 +1799,13 @@
       <c r="D39" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="3">
+      <c r="E39" s="1">
         <v>15</v>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="1">
         <v>1</v>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="1">
         <v>-1</v>
       </c>
     </row>
